--- a/reporte_prueba_v2.xlsx
+++ b/reporte_prueba_v2.xlsx
@@ -32,7 +32,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -47,7 +47,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFD9B3"/>
+        <fgColor rgb="00FFB3B3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B3FFB3"/>
       </patternFill>
     </fill>
   </fills>
@@ -63,11 +68,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,7 +457,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>200.67.0.0/24</t>
+          <t>200.67.0.0/21</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr"/>
@@ -459,12 +465,84 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>200.67.0.0/24</t>
+          <t>200.67.3.0/24</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>AUDITORIA</t>
+          <t>BLOQUEO</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>200.67.4.0/24</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>BLOQUEO</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>200.67.6.0/24</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>BLOQUEO</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>200.67.0.0/23</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>LIMPIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>200.67.2.0/24</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>LIMPIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>200.67.5.0/24</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>LIMPIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>200.67.7.0/24</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>LIMPIO</t>
         </is>
       </c>
     </row>
@@ -479,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,6 +569,42 @@
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Resultado</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>200.67.3.0/24</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BLOQUEO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>200.67.4.0/24</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BLOQUEO</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>200.67.6.0/24</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BLOQUEO</t>
         </is>
       </c>
     </row>
@@ -505,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,6 +631,66 @@
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Resultado</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>200.67.0.0/24</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LIMPIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>200.67.1.0/24</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LIMPIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>200.67.2.0/24</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LIMPIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>200.67.5.0/24</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LIMPIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>200.67.7.0/24</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LIMPIO</t>
         </is>
       </c>
     </row>
@@ -531,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -550,384 +724,6 @@
           <t>resultado</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>b.barracudacentral.org</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>dyna.spamrats.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>200.67.0.0/24</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>200.67.0.1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>AUDITORIA</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>200.67.0.0/24</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>200.67.0.162</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>AUDITORIA</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>200.67.0.0/24</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>200.67.0.166</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>AUDITORIA</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>200.67.0.0/24</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>200.67.0.167</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>AUDITORIA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>200.67.0.0/24</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>200.67.0.170</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>AUDITORIA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>200.67.0.0/24</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>200.67.0.174</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>AUDITORIA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>200.67.0.0/24</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>200.67.0.183</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AUDITORIA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>200.67.0.0/24</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>200.67.0.184</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AUDITORIA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>200.67.0.0/24</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>200.67.0.187</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AUDITORIA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>200.67.0.0/24</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>200.67.0.201</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AUDITORIA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>200.67.0.0/24</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>200.67.0.213</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AUDITORIA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>200.67.0.0/24</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>200.67.0.214</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AUDITORIA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>200.67.0.0/24</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>200.67.0.219</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>AUDITORIA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>200.67.0.0/24</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>200.67.0.222</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>AUDITORIA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>200.67.0.0/24</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>200.67.0.225</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>AUDITORIA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>200.67.0.0/24</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>200.67.0.241</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>AUDITORIA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
